--- a/gex_pivot_levels_2026-10-19.xlsx
+++ b/gex_pivot_levels_2026-10-19.xlsx
@@ -16,11 +16,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -800,12 +800,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-$8.53M</t>
+          <t>-$9.45M</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>+$9.01M</t>
+          <t>+$9.97M</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>-$2.02M</t>
+          <t>-$2.18M</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+$4.00M</t>
+          <t>+$4.33M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>-$34.94M</t>
+          <t>-$38.52M</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>+$53.42M</t>
+          <t>+$58.90M</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>+$4.60M</t>
+          <t>+$4.94M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>+$19.13M</t>
+          <t>+$20.56M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>-$3.67M</t>
+          <t>-$3.91M</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>+$10.74M</t>
+          <t>+$11.46M</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>+$5.31M</t>
+          <t>+$5.58M</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>+$51.33M</t>
+          <t>+$53.93M</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>+$1.38M</t>
+          <t>+$1.33M</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>+$22.33M</t>
+          <t>+$21.54M</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>+$6.40M</t>
+          <t>+$5.89M</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>+$24.66M</t>
+          <t>+$22.66M</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>+$736.07K</t>
+          <t>+$652.97K</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>+$32.52M</t>
+          <t>+$28.85M</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$12.90M</t>
+          <t>-$34.15M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$12.94M</t>
+          <t>+$34.97M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>29491.38</v>
+        <v>29409.14</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$637.51K</t>
+          <t>-$2.89M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$637.51K</t>
+          <t>+$3.60M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$5.52M</t>
+          <t>-$15.23M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$5.71M</t>
+          <t>+$16.20M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1618,166 +1618,166 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>29655.86</v>
+        <v>29658.45</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>707</v>
+        <v>29075</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-$4.09K</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>+$4.09K</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>29683.45</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>29100</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>-$277.87K</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+$318.73K</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>29693.45</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>29110</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>-$4.09K</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+$8.17K</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>29733.45</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>29150</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-$275.53K</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$340.91K</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>29738.1</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$1.41M</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$1.43M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$479.36K</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+$9.07M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>29658.45</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>29075</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>-$4.09K</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+$4.09K</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>29683.45</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>29100</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>-$277.87K</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$318.73K</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>29693.45</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>29110</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>-$4.09K</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+$8.17K</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>29733.45</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>29150</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>-$275.53K</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>+$340.91K</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-$9.54M</t>
+          <t>-$29.19M</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>+$9.88M</t>
+          <t>+$69.22M</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -2053,14 +2053,14 @@
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>-$1.80M</t>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>+$2.01M</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>+$1.90M</t>
+          <t>+$11.10M</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>-$8.40M</t>
+          <t>-$8.84M</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>+$8.94M</t>
+          <t>+$51.55M</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -2463,197 +2463,98 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="2" t="n">
         <v>30067.07</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="2" t="n">
         <v>717</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>-$846.77K</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>+$2.17M</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>+$8.38M</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>+$15.12M</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>30108.19</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="A38" s="5" t="n">
+        <v>30190.43</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>-$4.78M</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>+$5.76M</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>+$2.67M</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>+$25.45M</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>30149.31</v>
+        <v>30601.64</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>-$2.25M</t>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>+$4.89M</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>+$3.29M</t>
+          <t>+$7.68M</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>30190.43</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>-$12.87M</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>+$15.25M</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>30396.04</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>725</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>+$619.61K</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>+$3.88M</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>30519.4</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>728</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>-$869.83K</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>+$3.11M</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G42"/>
+  <autoFilter ref="A1:G39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3912,7 +3813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3970,324 +3871,328 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>29779.22</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-$29.19M</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>+$69.22M</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>7757.06</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>7650</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-$34.94M</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>+$53.42M</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-$38.52M</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>+$58.90M</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B4" s="5" t="n">
         <v>7807.06</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C4" s="5" t="n">
         <v>7700</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>+$5.31M</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>+$51.33M</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>+$5.58M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>+$53.93M</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>29984.83</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-$8.84M</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>+$51.55M</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>7804.13</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C6" s="2" t="n">
         <v>767</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>-$32.79M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>+$41.98M</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>29368.02</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-$34.15M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>+$34.97M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B8" s="5" t="n">
         <v>7857.06</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C8" s="5" t="n">
         <v>7750</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>+$736.07K</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>+$32.52M</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>+$652.97K</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>+$28.85M</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>7847.06</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>7740</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>+$6.40M</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>+$24.66M</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>7832.06</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7725</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>+$1.38M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>+$22.33M</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>7834.24</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-$11.78M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>+$22.00M</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>30190.43</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>+$2.67M</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>+$25.45M</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>7784.06</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>-$7.95M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>+$20.90M</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="B10" s="5" t="n">
+        <v>7847.06</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>7740</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>+$5.89M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>+$22.66M</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>7792.06</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>7685</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>+$4.60M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>+$19.13M</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4296,10 +4201,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7753.96</v>
+        <v>7834.24</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -4308,12 +4213,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-$13.91M</t>
+          <t>-$11.78M</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>+$15.99M</t>
+          <t>+$22.00M</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -4328,292 +4233,284 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>30190.43</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-$12.87M</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>+$15.25M</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>7832.06</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7725</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>+$1.33M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+$21.54M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>29368.02</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-$12.90M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>+$12.94M</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7784.06</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-$7.95M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+$20.90M</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>7733.89</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>760</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>-$10.35M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+$11.71M</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="B14" s="2" t="n">
+        <v>7792.06</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>7685</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$4.94M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+$20.56M</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>29573.62</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-$15.23M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>+$16.20M</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>7703.78</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>757</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="B16" s="2" t="n">
+        <v>7753.96</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>762</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-$10.92M</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>+$11.57M</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-$13.91M</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>+$15.99M</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>30067.07</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>+$8.38M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>+$15.12M</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>7824.2</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>769</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="B18" s="5" t="n">
+        <v>7733.89</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>760</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>-$3.77M</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>+$11.01M</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>7802.06</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>7695</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>-$3.67M</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>+$10.74M</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>7633.53</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-$10.49M</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>+$10.74M</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-$10.35M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>+$11.71M</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>29779.22</v>
+        <v>7703.78</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>710</v>
+        <v>757</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>-$9.54M</t>
+          <t>-$10.92M</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>+$9.88M</t>
+          <t>+$11.57M</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4634,146 +4531,150 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>7774.03</v>
+        <v>7802.06</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>764</v>
+        <v>7695</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>-$3.91M</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>+$11.46M</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>29820.35</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>711</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>+$2.01M</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>+$11.10M</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>7824.2</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>769</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>-$3.89M</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>+$9.32M</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-$3.77M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>+$11.01M</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>7737.06</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>7630</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>-$8.53M</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>+$9.01M</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="B23" s="2" t="n">
+        <v>7633.53</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>-$10.49M</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>+$10.74M</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>29984.83</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>715</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>-$8.40M</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>+$8.94M</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>2746.38</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>-$2.28M</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>+$8.79M</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4782,24 +4683,24 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7603.43</v>
+        <v>7737.06</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>747</v>
+        <v>7630</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>-$8.09M</t>
+          <t>-$9.45M</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>+$8.37M</t>
+          <t>+$9.97M</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4816,28 +4717,28 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>2736.32</v>
+        <v>7774.03</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>272</v>
+        <v>764</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>-$6.01M</t>
+          <t>-$3.89M</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>+$7.20M</t>
+          <t>+$9.32M</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -4847,157 +4748,153 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7673.67</v>
+        <v>29738.1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>754</v>
+        <v>709</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>-$5.78M</t>
+          <t>-$479.36K</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>+$6.43M</t>
+          <t>+$9.07M</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2746.38</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>-$2.28M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+$8.79M</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>2716.2</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>270</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>-$4.92M</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>+$6.01M</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7603.43</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>-$8.09M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+$8.37M</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>30108.19</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="B29" s="5" t="n">
+        <v>30601.64</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>730</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>-$4.78M</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>+$5.76M</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>29573.62</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>705</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-$5.52M</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>+$5.71M</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>+$4.89M</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>+$7.68M</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5006,24 +4903,24 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2766.5</v>
+        <v>2736.32</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>+$654.20K</t>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>-$6.01M</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>+$4.29M</t>
+          <t>+$7.20M</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -5033,145 +4930,145 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>7673.67</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>754</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>-$5.78M</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>+$6.43M</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>2726.26</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>271</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="B32" s="2" t="n">
+        <v>2716.2</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>-$2.54M</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>+$4.12M</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>7752.06</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>7645</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>-$2.02M</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>+$4.00M</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>-$4.92M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>+$6.01M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>30396.04</v>
+        <v>7752.06</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>725</v>
+        <v>7645</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>+$619.61K</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>-$2.18M</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>+$3.88M</t>
+          <t>+$4.33M</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>7713.81</v>
+        <v>2766.5</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>758</v>
+        <v>275</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>-$2.82M</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>+$654.20K</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>+$3.39M</t>
+          <t>+$4.29M</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -5188,28 +5085,28 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>30149.31</v>
+        <v>2726.26</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>719</v>
+        <v>271</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-$2.25M</t>
+          <t>-$2.54M</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>+$3.29M</t>
+          <t>+$4.12M</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -5230,10 +5127,10 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>30519.4</v>
+        <v>29409.14</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
@@ -5242,168 +5139,172 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>-$869.83K</t>
+          <t>-$2.89M</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>+$3.11M</t>
+          <t>+$3.60M</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>7713.81</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>758</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>-$2.82M</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>+$3.39M</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B38" s="5" t="n">
         <v>2776.56</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="5" t="n">
         <v>276</v>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>-$1.16M</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>+$2.50M</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>4255.98</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C39" s="2" t="n">
         <v>387</v>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>+$2.33M</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>+$2.45M</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>4179</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>+$1.68M</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>+$2.41M</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>30067.07</v>
+        <v>4179</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>717</v>
+        <v>380</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>-$846.77K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>+$1.68M</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>+$2.17M</t>
+          <t>+$2.41M</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -5522,28 +5423,28 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>29820.35</v>
+        <v>7643.57</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>711</v>
+        <v>751</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>-$1.80M</t>
+          <t>-$1.03M</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>+$1.90M</t>
+          <t>+$1.77M</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -5558,114 +5459,114 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>4211.99</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>+$1.40M</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>+$1.46M</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>7643.57</v>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>751</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="B46" s="5" t="n">
+        <v>7613.46</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-$1.03M</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>+$1.77M</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>-$744.86K</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>+$1.46M</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>4211.99</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>383</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>+$1.40M</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>+$1.46M</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>7613.46</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>748</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>-$744.86K</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>+$1.46M</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="B47" s="2" t="n">
+        <v>4167.09</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>+$1.31M</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>+$1.43M</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5674,28 +5575,28 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>29655.86</v>
+        <v>4200.99</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>707</v>
+        <v>382</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>-$1.41M</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>+$868.60K</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>+$1.43M</t>
+          <t>+$1.19M</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -5705,7 +5606,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -5716,24 +5617,24 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4167.09</v>
+        <v>4135.01</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>87</v>
+        <v>376</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>+$1.31M</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>-$967.32K</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>+$1.43M</t>
+          <t>+$1.04M</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5743,7 +5644,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -5754,10 +5655,10 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>4200.99</v>
+        <v>4222.98</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -5766,12 +5667,12 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>+$868.60K</t>
+          <t>+$632.77K</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>+$1.19M</t>
+          <t>+$880.54K</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -5786,182 +5687,178 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>4135.01</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>376</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="B51" s="5" t="n">
+        <v>4244.98</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>386</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>-$967.32K</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>+$1.04M</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>+$720.30K</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>+$801.99K</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>-$715.80K</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$791.67K</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>4222.98</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>384</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="B53" s="2" t="n">
+        <v>4310.79</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>+$723.80K</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>+$769.81K</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>4288.97</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>+$632.77K</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$880.54K</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>4244.98</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>386</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>+$720.30K</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>+$801.99K</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>90.28</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>-$715.80K</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>+$791.67K</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>+$629.74K</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>+$721.31K</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>4310.79</v>
+        <v>96.3</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>+$723.80K</t>
+          <t>+$578.55K</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>+$769.81K</t>
+          <t>+$642.09K</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5976,102 +5873,102 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>4288.97</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>390</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>+$629.74K</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>+$721.31K</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>+$583.04K</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>+$611.07K</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-$70.11K</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>+$551.67K</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>+$578.55K</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>+$642.09K</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>29491.38</v>
+        <v>4124.01</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>703</v>
+        <v>375</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-$637.51K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>+$109.33K</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>+$637.51K</t>
+          <t>+$550.78K</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -6086,38 +5983,38 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B59" s="5" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>+$583.04K</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>+$611.07K</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>+$296.02K</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>+$451.31K</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -6130,10 +6027,10 @@
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>93.29000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
@@ -6142,134 +6039,134 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>-$70.11K</t>
+          <t>-$164.61K</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+$551.67K</t>
+          <t>+$375.21K</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>4124.01</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>+$109.33K</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>+$550.78K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>29733.45</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>29150</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>-$275.53K</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>+$340.91K</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>93.89</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>+$296.02K</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>+$451.31K</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>29783.45</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>29200</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>-$189.14K</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>+$338.58K</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>94.5</v>
+        <v>4332.96</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>157</v>
+        <v>394</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-$164.61K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>+$312.31K</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>+$375.21K</t>
+          <t>+$323.72K</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -6278,10 +6175,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>29733.45</v>
+        <v>29683.45</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>29150</v>
+        <v>29100</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -6290,12 +6187,12 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>-$275.53K</t>
+          <t>-$277.87K</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>+$340.91K</t>
+          <t>+$318.73K</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -6316,10 +6213,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>29783.45</v>
+        <v>29763.45</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>29200</v>
+        <v>29180</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -6328,12 +6225,12 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>-$189.14K</t>
+          <t>-$254.52K</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>+$338.58K</t>
+          <t>+$305.89K</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6348,38 +6245,42 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>4332.96</v>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>394</v>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>+$312.31K</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>+$323.72K</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>29843.45</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>29260</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>-$245.18K</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>+$259.19K</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -6388,10 +6289,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>29683.45</v>
+        <v>29813.45</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>29100</v>
+        <v>29230</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -6400,12 +6301,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>-$277.87K</t>
+          <t>-$240.51K</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>+$318.73K</t>
+          <t>+$259.19K</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -6422,28 +6323,28 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>29763.45</v>
+        <v>83.06</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>29180</v>
+        <v>138</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>-$254.52K</t>
+          <t>-$218.96K</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>+$305.89K</t>
+          <t>+$238.08K</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6458,76 +6359,72 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>29843.45</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>29260</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>-$245.18K</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>+$259.19K</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>-$34.26K</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>+$202.03K</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>29813.45</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>29230</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>-$240.51K</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>+$259.19K</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>4214.99</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>+$5.97K</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>+$180.02K</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -6536,28 +6433,28 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>83.06</v>
+        <v>29583.45</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>138</v>
+        <v>29000</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>-$218.96K</t>
+          <t>-$79.68K</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>+$238.08K</t>
+          <t>+$132.80K</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -6578,24 +6475,24 @@
         </is>
       </c>
       <c r="B72" s="5" t="n">
-        <v>92.09</v>
+        <v>100.51</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>-$34.26K</t>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>+$114.60K</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>+$202.03K</t>
+          <t>+$115.89K</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -6608,254 +6505,258 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>4214.99</v>
+        <v>29883.45</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>88</v>
+        <v>29300</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>+$5.97K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-$39.70K</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>+$180.02K</t>
+          <t>+$114.42K</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>29753.45</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>29170</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>+$4.67K</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>+$102.74K</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>29863.45</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>29280</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-$91.07K</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>+$95.74K</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>29933.45</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>29350</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>-$51.37K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$93.40K</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>29958.45</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>29375</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>-$67.72K</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>+$91.07K</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>29773.45</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>29190</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>-$28.02K</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>+$84.06K</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>29583.45</v>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="B79" s="5" t="n">
+        <v>29823.45</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>29240</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>-$79.68K</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>+$132.80K</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>100.51</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>+$114.60K</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>+$115.89K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>29883.45</v>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>29300</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-$39.70K</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>+$114.42K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>29753.45</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>29170</v>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>+$4.67K</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>+$102.74K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="n">
-        <v>29863.45</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>29280</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>-$91.07K</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>+$95.74K</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="n">
-        <v>29933.45</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>29350</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-$51.37K</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>+$93.40K</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-$72.39K</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>+$81.73K</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -6866,10 +6767,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>29958.45</v>
+        <v>29633.45</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>29375</v>
+        <v>29050</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -6878,12 +6779,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>-$67.72K</t>
+          <t>-$69.47K</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>+$91.07K</t>
+          <t>+$69.47K</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6900,112 +6801,112 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>+$2.34K</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>+$64.05K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n">
-        <v>29773.45</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>29190</v>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="B82" s="2" t="n">
+        <v>29653.45</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>29070</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>-$28.02K</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>+$84.06K</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>-$46.99K</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>+$59.25K</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>+$52.36K</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>+$53.97K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>29823.45</v>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>29240</v>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>-$72.39K</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>+$81.73K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>29633.45</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>29050</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-$69.47K</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>+$69.47K</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -7014,104 +6915,100 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>87.27</v>
+        <v>29908.45</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>145</v>
+        <v>29325</v>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>+$2.34K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-$25.69K</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>+$64.05K</t>
+          <t>+$53.71K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>29793.45</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>29210</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>-$9.34K</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>+$42.03K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>29653.45</v>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>29070</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>-$46.99K</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>+$59.25K</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>97.81</v>
+        <v>29858.45</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>162.5</v>
+        <v>29275</v>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>+$52.36K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-$39.70K</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>+$53.97K</t>
+          <t>+$39.70K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -7121,7 +7018,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -7132,32 +7029,36 @@
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>29908.45</v>
+        <v>29758.45</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>29325</v>
+        <v>29175</v>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>-$25.69K</t>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>+$4.67K</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>+$53.71K</t>
+          <t>+$32.69K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -7166,24 +7067,24 @@
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>29793.45</v>
+        <v>29953.45</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>29210</v>
+        <v>29370</v>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>-$9.34K</t>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>+$4.67K</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>+$42.03K</t>
+          <t>+$32.69K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -7204,10 +7105,10 @@
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>29858.45</v>
+        <v>29613.45</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>29275</v>
+        <v>29030</v>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
@@ -7216,24 +7117,20 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>-$39.70K</t>
+          <t>-$32.69K</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>+$39.70K</t>
+          <t>+$32.69K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -7242,24 +7139,24 @@
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>29758.45</v>
+        <v>29973.45</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>29175</v>
+        <v>29390</v>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>+$4.67K</t>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>-$9.34K</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>+$32.69K</t>
+          <t>+$23.35K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -7280,10 +7177,10 @@
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>29953.45</v>
+        <v>29923.45</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>29370</v>
+        <v>29340</v>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
@@ -7292,12 +7189,12 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>+$4.67K</t>
+          <t>+$2.34K</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>+$32.69K</t>
+          <t>+$11.68K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -7318,10 +7215,10 @@
         </is>
       </c>
       <c r="B92" s="5" t="n">
-        <v>29613.45</v>
+        <v>29693.45</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>29030</v>
+        <v>29110</v>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
@@ -7330,20 +7227,24 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>-$32.69K</t>
+          <t>-$4.09K</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>+$32.69K</t>
+          <t>+$8.17K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -7352,24 +7253,24 @@
         </is>
       </c>
       <c r="B93" s="5" t="n">
-        <v>29973.45</v>
+        <v>29643.45</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>29390</v>
+        <v>29060</v>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>-$9.34K</t>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>$0</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>+$23.35K</t>
+          <t>+$4.09K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -7390,24 +7291,24 @@
         </is>
       </c>
       <c r="B94" s="5" t="n">
-        <v>29923.45</v>
+        <v>29658.45</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>29340</v>
+        <v>29075</v>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>+$2.34K</t>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>-$4.09K</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>+$11.68K</t>
+          <t>+$4.09K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -7428,10 +7329,10 @@
         </is>
       </c>
       <c r="B95" s="5" t="n">
-        <v>29693.45</v>
+        <v>29623.45</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>29110</v>
+        <v>29040</v>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
@@ -7440,12 +7341,12 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>-$4.09K</t>
+          <t>-$2.04K</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>+$8.17K</t>
+          <t>+$2.04K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -7459,122 +7360,8 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>29643.45</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>29060</v>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>+$4.09K</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>29658.45</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>29075</v>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>-$4.09K</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>+$4.09K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="n">
-        <v>29623.45</v>
-      </c>
-      <c r="C98" s="5" t="n">
-        <v>29040</v>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>-$2.04K</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>+$2.04K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H98"/>
+  <autoFilter ref="A1:H95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>